--- a/data/analysis_panns/sound_event_eval_panns_w2_5s_h1_25s.xlsx
+++ b/data/analysis_panns/sound_event_eval_panns_w2_5s_h1_25s.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="29">
   <si>
     <t>event</t>
   </si>
@@ -81,49 +81,40 @@
     <t>NO</t>
   </si>
   <si>
-    <t>speech(0-90), animal(60-240), horse(120-180), engine(150-210)</t>
-  </si>
-  <si>
-    <t>speech(0-210), animal(180-240)</t>
-  </si>
-  <si>
-    <t>speech(0-210), animal(120-180), engine(180-240)</t>
+    <t>engine(150-210)</t>
+  </si>
+  <si>
+    <t>engine(180-240)</t>
   </si>
   <si>
     <t>YES</t>
   </si>
   <si>
-    <t>speech(0-120), burst_pop(90-150), gunshot_or_explosion(120-180), engine(150-240)</t>
-  </si>
-  <si>
-    <t>engine(0-60), burst_pop(30-90), gunshot_or_explosion(60-120), speech(90-240)</t>
-  </si>
-  <si>
-    <t>engine(0-60), speech(30-150), gunshot_or_explosion(120-180), engine(150-240)</t>
-  </si>
-  <si>
-    <t>gunshot_or_explosion(0-90), engine(60-120), speech(90-210), engine(180-240)</t>
-  </si>
-  <si>
-    <t>gunshot_or_explosion(0-90), speech(60-150), engine(120-240)</t>
-  </si>
-  <si>
-    <t>door(0-90), engine(60-240)</t>
-  </si>
-  <si>
-    <t>tick_tock(0-60), shuffle(30-90), engine(60-240)</t>
-  </si>
-  <si>
-    <t>animal(0-60), door(30-90), engine(60-240)</t>
-  </si>
-  <si>
-    <t>horn(0-90), breaking(60-150), engine(120-210), door(180-240)</t>
-  </si>
-  <si>
-    <t>engine(0-60), skidding(30-90), gunshot_or_explosion(60-120), glass_breaking(90-150), speech(120-240)</t>
-  </si>
-  <si>
-    <t>horn(0-60), engine(30-240), gunshot_or_explosion(60-120), breaking(90-150)</t>
+    <t>gunshot_or_explosion(90-180), engine(150-240)</t>
+  </si>
+  <si>
+    <t>engine(0-60), gunshot_or_explosion(30-120)</t>
+  </si>
+  <si>
+    <t>engine(0-60), gunshot_or_explosion(120-180), engine(150-240)</t>
+  </si>
+  <si>
+    <t>gunshot_or_explosion(0-90), engine(60-120), engine(180-240)</t>
+  </si>
+  <si>
+    <t>gunshot_or_explosion(0-90), engine(120-240)</t>
+  </si>
+  <si>
+    <t>engine(60-240)</t>
+  </si>
+  <si>
+    <t>horn(0-90), engine(120-210)</t>
+  </si>
+  <si>
+    <t>engine(0-60), skidding(30-90), gunshot_or_explosion(60-120), glass_breaking(90-150)</t>
+  </si>
+  <si>
+    <t>horn(0-60), engine(30-240), gunshot_or_explosion(60-120)</t>
   </si>
 </sst>
 </file>
@@ -655,6 +646,138 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
         <v>26</v>
       </c>
     </row>
@@ -663,175 +786,43 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
-        <v>6</v>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
       </c>
       <c r="E2" t="s">
         <v>27</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>16</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -842,13 +833,13 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -892,7 +883,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -903,13 +894,13 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -996,6 +987,47 @@
       <c r="D2" t="s">
         <v>6</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
       <c r="E2" t="s">
         <v>18</v>
       </c>
@@ -1005,7 +1037,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1029,57 +1061,57 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
         <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
       </c>
       <c r="D2" t="s">
         <v>4</v>
@@ -1093,7 +1125,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1117,13 +1149,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
-        <v>20</v>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
       </c>
       <c r="D2" t="s">
         <v>4</v>
@@ -1137,7 +1169,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1161,13 +1193,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
+      <c r="C2" t="s">
+        <v>19</v>
       </c>
       <c r="D2" t="s">
         <v>4</v>
@@ -1181,7 +1213,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1205,13 +1237,13 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
         <v>4</v>
@@ -1223,48 +1255,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/data/analysis_panns/sound_event_eval_panns_w2_5s_h1_25s.xlsx
+++ b/data/analysis_panns/sound_event_eval_panns_w2_5s_h1_25s.xlsx
@@ -22,13 +22,19 @@
     <sheet name="Scene_15" sheetId="13" r:id="rId13"/>
     <sheet name="Scene_16" sheetId="14" r:id="rId14"/>
     <sheet name="Scene_17" sheetId="15" r:id="rId15"/>
+    <sheet name="Scene_29" sheetId="16" r:id="rId16"/>
+    <sheet name="Scene_30" sheetId="17" r:id="rId17"/>
+    <sheet name="Scene_31" sheetId="18" r:id="rId18"/>
+    <sheet name="Scene_32" sheetId="19" r:id="rId19"/>
+    <sheet name="Scene_33" sheetId="20" r:id="rId20"/>
+    <sheet name="Scene_34" sheetId="21" r:id="rId21"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="31">
   <si>
     <t>event</t>
   </si>
@@ -115,6 +121,12 @@
   </si>
   <si>
     <t>horn(0-60), engine(30-240), gunshot_or_explosion(60-120)</t>
+  </si>
+  <si>
+    <t>engine(90-240)</t>
+  </si>
+  <si>
+    <t>skidding(0-90)</t>
   </si>
 </sst>
 </file>
@@ -908,6 +920,176 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
@@ -952,6 +1134,94 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
